--- a/ig/ch-core/StructureDefinition-ch-core-allergyintolerance.xlsx
+++ b/ig/ch-core/StructureDefinition-ch-core-allergyintolerance.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>6.0.0</t>
+    <t>7.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T08:02:49+00:00</t>
+    <t>2026-06-10T15:05:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -911,7 +911,7 @@
     <t>certainty</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {allergyintolerance-certainty|5.3.0-ballot-tc1}
+    <t xml:space="preserve">Extension {allergyintolerance-certainty|5.3.0}
 </t>
   </si>
   <si>
@@ -937,7 +937,7 @@
     <t>duration</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {allergyintolerance-duration|5.3.0-ballot-tc1}
+    <t xml:space="preserve">Extension {allergyintolerance-duration|5.3.0}
 </t>
   </si>
   <si>
@@ -953,7 +953,7 @@
     <t>location</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {openEHR-location|5.3.0-ballot-tc1}
+    <t xml:space="preserve">Extension {openEHR-location|5.3.0}
 </t>
   </si>
   <si>
@@ -969,7 +969,7 @@
     <t>exposureDate</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {openEHR-exposureDate|5.3.0-ballot-tc1}
+    <t xml:space="preserve">Extension {openEHR-exposureDate|5.3.0}
 </t>
   </si>
   <si>
@@ -988,7 +988,7 @@
     <t>exposureDuration</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {openEHR-exposureDuration|5.3.0-ballot-tc1}
+    <t xml:space="preserve">Extension {openEHR-exposureDuration|5.3.0}
 </t>
   </si>
   <si>
@@ -1004,7 +1004,7 @@
     <t>exposureDescription</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {openEHR-exposureDescription|5.3.0-ballot-tc1}
+    <t xml:space="preserve">Extension {openEHR-exposureDescription|5.3.0}
 </t>
   </si>
   <si>
@@ -1020,7 +1020,7 @@
     <t>management</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {openEHR-management|5.3.0-ballot-tc1}
+    <t xml:space="preserve">Extension {openEHR-management|5.3.0}
 </t>
   </si>
   <si>
